--- a/Baseline_Chunking/eval_result/Overall_Result.xlsx
+++ b/Baseline_Chunking/eval_result/Overall_Result.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\repo\TechTrojan\AdvanceRAG\Baseline_Chunking\eval_result\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{091D130C-4DE9-4FE6-9D2E-524320398720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC3A7E2-9E96-428F-811D-BDA592FD1E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4CC848F3-F6A2-4383-8D8B-AA33B4736383}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4CC848F3-F6A2-4383-8D8B-AA33B4736383}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>context_adherence</t>
   </si>
@@ -99,6 +99,32 @@
   </si>
   <si>
     <t>Hybrid  + Reranking</t>
+  </si>
+  <si>
+    <t>Chunk 
+Overlap</t>
+  </si>
+  <si>
+    <t>Chunk 
+Size</t>
+  </si>
+  <si>
+    <t>No. of semantic document retrieval</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Keyword Search
+Weight</t>
+  </si>
+  <si>
+    <t>Vector Search
+Weight</t>
+  </si>
+  <si>
+    <t>Hybrid documents 
+return</t>
   </si>
 </sst>
 </file>
@@ -259,7 +285,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -280,12 +306,123 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="17">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -438,14 +575,16 @@
     </dxf>
     <dxf>
       <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
+        <left/>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top/>
-        <bottom/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
@@ -455,37 +594,10 @@
       </border>
     </dxf>
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
         </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -522,6 +634,31 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -536,15 +673,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BEBC2C6A-080F-47C5-94F1-5B0F0A0EE61E}" name="Table1" displayName="Table1" ref="A1:F9" totalsRowShown="0" headerRowDxfId="5" dataDxfId="10" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7" dataCellStyle="Percent">
-  <autoFilter ref="A1:F9" xr:uid="{BEBC2C6A-080F-47C5-94F1-5B0F0A0EE61E}"/>
-  <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{CEFF12AF-4884-4DBF-943D-8C7FA16A245E}" name="Design" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{B7943A73-59F3-44D2-8048-9235BA8367DF}" name="Description" dataDxfId="4"/>
-    <tableColumn id="3" xr3:uid="{E58D75B5-9B24-4E6D-ADDD-0C72054FF087}" name="context_adherence" dataDxfId="3" dataCellStyle="Percent"/>
-    <tableColumn id="4" xr3:uid="{338395D1-C71C-48F1-8F82-2D521839606A}" name="context_precision" dataDxfId="2" dataCellStyle="Percent"/>
-    <tableColumn id="5" xr3:uid="{F55E9C67-4028-4FAC-B96A-CFAC1DD7CF71}" name="answer_relevance" dataDxfId="1" dataCellStyle="Percent"/>
-    <tableColumn id="6" xr3:uid="{85F8047E-3FDE-48DD-B543-DB6EB50DE522}" name="groundedness.score" dataDxfId="0" dataCellStyle="Percent"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BEBC2C6A-080F-47C5-94F1-5B0F0A0EE61E}" name="Table1" displayName="Table1" ref="A1:L9" totalsRowShown="0" headerRowDxfId="16" dataDxfId="14" headerRowBorderDxfId="15" tableBorderDxfId="13" totalsRowBorderDxfId="12" dataCellStyle="Percent">
+  <autoFilter ref="A1:L9" xr:uid="{BEBC2C6A-080F-47C5-94F1-5B0F0A0EE61E}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{CEFF12AF-4884-4DBF-943D-8C7FA16A245E}" name="Design" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{B7943A73-59F3-44D2-8048-9235BA8367DF}" name="Description" dataDxfId="10"/>
+    <tableColumn id="7" xr3:uid="{C0F9E952-3CFC-4206-8B83-E59A1C9E77B5}" name="Chunk _x000a_Size" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{133DA3C0-9E98-4C75-AB49-5C10177DA4C4}" name="Chunk _x000a_Overlap" dataDxfId="4"/>
+    <tableColumn id="10" xr3:uid="{D0CC75FD-5AEE-40EF-B5C5-70CEF18119E0}" name="No. of semantic document retrieval" dataDxfId="2"/>
+    <tableColumn id="12" xr3:uid="{B96719A0-277B-4BDC-B47C-7421F388FE24}" name="Hybrid documents _x000a_return" dataDxfId="0"/>
+    <tableColumn id="11" xr3:uid="{F2D34A72-FB85-4D3B-8FB9-39CE82BBFAC2}" name="Keyword Search_x000a_Weight" dataDxfId="1"/>
+    <tableColumn id="9" xr3:uid="{6FC147AF-4EC4-4B57-AF59-87AF19363796}" name="Vector Search_x000a_Weight" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{E58D75B5-9B24-4E6D-ADDD-0C72054FF087}" name="context_adherence" dataDxfId="9" dataCellStyle="Percent"/>
+    <tableColumn id="4" xr3:uid="{338395D1-C71C-48F1-8F82-2D521839606A}" name="context_precision" dataDxfId="8" dataCellStyle="Percent"/>
+    <tableColumn id="5" xr3:uid="{F55E9C67-4028-4FAC-B96A-CFAC1DD7CF71}" name="answer_relevance" dataDxfId="7" dataCellStyle="Percent"/>
+    <tableColumn id="6" xr3:uid="{85F8047E-3FDE-48DD-B543-DB6EB50DE522}" name="groundedness.score" dataDxfId="6" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium12" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -867,194 +1010,358 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{876212AF-7B40-409D-93F2-6D9C0A2509E6}">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="36.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.85546875" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.5703125" customWidth="1"/>
+    <col min="11" max="11" width="18.85546875" customWidth="1"/>
+    <col min="12" max="12" width="21.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="8">
+      <c r="C2" s="5">
+        <v>1000</v>
+      </c>
+      <c r="D2" s="5">
+        <v>200</v>
+      </c>
+      <c r="E2" s="5">
+        <v>5</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="I2" s="8">
         <v>0.80952380952380953</v>
       </c>
-      <c r="D2" s="8">
+      <c r="J2" s="8">
         <v>0.45714285714285713</v>
       </c>
-      <c r="E2" s="8">
+      <c r="K2" s="8">
         <v>0.69823809523809532</v>
       </c>
-      <c r="F2" s="9">
+      <c r="L2" s="9">
         <v>0.76190476190476186</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="8">
+      <c r="C3" s="5">
+        <v>600</v>
+      </c>
+      <c r="D3" s="5">
+        <v>60</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="8">
         <v>0.84761904761904761</v>
       </c>
-      <c r="D3" s="8">
+      <c r="J3" s="8">
         <v>0.47619047619047616</v>
       </c>
-      <c r="E3" s="8">
+      <c r="K3" s="8">
         <v>0.74480952380952381</v>
       </c>
-      <c r="F3" s="9">
+      <c r="L3" s="9">
         <v>0.74603174604761913</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="5">
+        <v>600</v>
+      </c>
+      <c r="D4" s="5">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5">
+        <v>10</v>
+      </c>
+      <c r="F4" s="5">
+        <v>5</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I4" s="8">
         <v>0.90476190476190477</v>
       </c>
-      <c r="D4" s="8">
+      <c r="J4" s="8">
         <v>0.40334467109523814</v>
       </c>
-      <c r="E4" s="8">
+      <c r="K4" s="8">
         <v>0.76285714285714279</v>
       </c>
-      <c r="F4" s="9">
+      <c r="L4" s="9">
         <v>0.80952380952380953</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="5">
+        <v>600</v>
+      </c>
+      <c r="D5" s="5">
+        <v>60</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5</v>
+      </c>
+      <c r="F5" s="5">
+        <v>5</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I5" s="8">
         <v>0.80952380952380953</v>
       </c>
-      <c r="D5" s="8">
+      <c r="J5" s="8">
         <v>0.39047619047619042</v>
       </c>
-      <c r="E5" s="8">
+      <c r="K5" s="8">
         <v>0.71719047619047627</v>
       </c>
-      <c r="F5" s="9">
+      <c r="L5" s="9">
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="5">
+        <v>600</v>
+      </c>
+      <c r="D6" s="5">
+        <v>60</v>
+      </c>
+      <c r="E6" s="5">
+        <v>5</v>
+      </c>
+      <c r="F6" s="5">
+        <v>5</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="I6" s="8">
         <v>0.75238095199999999</v>
       </c>
-      <c r="D6" s="8">
+      <c r="J6" s="8">
         <v>0.47619047599999997</v>
       </c>
-      <c r="E6" s="8">
+      <c r="K6" s="8">
         <v>0.67228571400000003</v>
       </c>
-      <c r="F6" s="9">
+      <c r="L6" s="9">
         <v>0.69841269800000005</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8">
+      <c r="C7" s="5">
+        <v>600</v>
+      </c>
+      <c r="D7" s="5">
+        <v>60</v>
+      </c>
+      <c r="E7" s="5">
+        <v>10</v>
+      </c>
+      <c r="F7" s="5">
+        <v>10</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0.6</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.4</v>
+      </c>
+      <c r="I7" s="8">
         <v>0.8571428571428571</v>
       </c>
-      <c r="D7" s="8">
+      <c r="J7" s="8">
         <v>0.41524943310657569</v>
       </c>
-      <c r="E7" s="8">
+      <c r="K7" s="8">
         <v>0.76604761904761909</v>
       </c>
-      <c r="F7" s="9">
+      <c r="L7" s="9">
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="5">
+        <v>600</v>
+      </c>
+      <c r="D8" s="5">
+        <v>60</v>
+      </c>
+      <c r="E8" s="5">
+        <v>5</v>
+      </c>
+      <c r="F8" s="5">
+        <v>10</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="I8" s="8">
         <v>0.8571428571428571</v>
       </c>
-      <c r="D8" s="8">
+      <c r="J8" s="8">
         <v>0.48571428571428565</v>
       </c>
-      <c r="E8" s="8">
+      <c r="K8" s="8">
         <v>0.71971428571428586</v>
       </c>
-      <c r="F8" s="9">
+      <c r="L8" s="9">
         <v>0.7142857142857143</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="10">
+      <c r="C9" s="5">
+        <v>600</v>
+      </c>
+      <c r="D9" s="5">
+        <v>60</v>
+      </c>
+      <c r="E9" s="7">
+        <v>10</v>
+      </c>
+      <c r="F9" s="7">
+        <v>10</v>
+      </c>
+      <c r="G9" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.5</v>
+      </c>
+      <c r="I9" s="10">
         <v>0.90476190476190477</v>
       </c>
-      <c r="D9" s="10">
+      <c r="J9" s="10">
         <v>0.37142857142857139</v>
       </c>
-      <c r="E9" s="10">
+      <c r="K9" s="10">
         <v>0.77061904761904765</v>
       </c>
-      <c r="F9" s="11">
+      <c r="L9" s="11">
         <v>0.80952380952380953</v>
       </c>
     </row>
